--- a/declarations_generes/DECLARATION_JUIN_2026.xlsx
+++ b/declarations_generes/DECLARATION_JUIN_2026.xlsx
@@ -83,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -99,6 +99,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -464,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -580,30 +581,82 @@
       <c r="F5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>BL82455FC</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Carat S.a.r.l</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="n">
+        <v>1071</v>
+      </c>
+      <c r="L5" s="7" t="n">
+        <v>203.49</v>
+      </c>
+      <c r="M5" s="7" t="n">
+        <v>1274.49</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>BLCDFCD7A</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Carat S.a.r.l</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="n">
+        <v>1071</v>
+      </c>
+      <c r="L6" s="7" t="n">
+        <v>203.49</v>
+      </c>
+      <c r="M6" s="7" t="n">
+        <v>1274.49</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="6" t="n">
-        <v>0</v>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="6" t="n">
+        <v>2142</v>
+      </c>
+      <c r="L7" s="6" t="n">
+        <v>406.98</v>
+      </c>
+      <c r="M7" s="6" t="n">
+        <v>2548.98</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A5:C5"/>
-    <mergeCell ref="H5:J5"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="H3:M3"/>
+    <mergeCell ref="H7:J7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
